--- a/series_data/viral-detective/series_log.xlsx
+++ b/series_data/viral-detective/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,510 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Kaan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sadaltager</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/36199fbf1c4d524cdb2f05da969f5ba0_1781557511.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mira</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>kore</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/99a6666d31ab7c1f31354ce5a7feb3b5_1781557943.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mira</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>kore</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a907724bc740d5b8d93653a794b83f55_1781558124.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mira, Deniz</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>leda</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e3e415d1388581edd59cb0a0c1cdd5a9_1781558265.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Kaan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sadaltager, orus</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/74672a8869e3ee5b538001ba55689345_1781558509.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Deniz</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>leda</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e747b7c716012683ee2719188ab4928e_1781558801.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Detective İhsan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>orus</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b40f17f50bab4751e26c8d10a2595a9c_1781558939.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_07.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-15 21:31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Detective İhsan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>orus</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2f70056c8c24167524df45e846cca8b_1781559093.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep02/shots/shot_08.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/viral-detective/series_log.xlsx
+++ b/series_data/viral-detective/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,6 +1699,510 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:44</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Deniz</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>orus, leda</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2dbf6c7950d1f002ca53432917945a67_1781635456.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:48</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Kaan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sadaltager, orus</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/807c40ba7fb49880b549ec150e6b971c_1781635709.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:50</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Deniz</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>leda</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d617d7f424b062e97a1f33634503560b_1781635846.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Kaan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>orus, sadaltager</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b3345e0ff0c67655c28e3832a5b58417_1781636135.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:58</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Detective İhsan, Mira</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>kore, orus</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/13b666deae705cba104a4b9522c42661_1781636284.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Detective İhsan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>orus</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/41a372ee5d5269155e2376fdd1125f65_1781636412.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Detective İhsan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>orus</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/546bb3a375d5fb560ee6faf248f823a4_1781636554.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_07.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Detective İhsan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>orus</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0218f46315358e789db9b090cddb40de_1781636699.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/viral-detective/episodes/ep03/shots/shot_08.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
